--- a/eksperimen/eks4_nocekout_prob1/perbandingan_split_70vs80.xlsx
+++ b/eksperimen/eks4_nocekout_prob1/perbandingan_split_70vs80.xlsx
@@ -617,16 +617,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7188</v>
+        <v>0.7232</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5591</v>
+        <v>0.5652</v>
       </c>
       <c r="F7" t="n">
         <v>0.7027</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6228</v>
+        <v>0.6264999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -671,16 +671,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.7321</v>
+        <v>0.7188</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5729</v>
+        <v>0.5567</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7432</v>
+        <v>0.7297</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6471</v>
+        <v>0.6316000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -887,13 +887,13 @@
         <v>0.7383</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5574</v>
+        <v>0.5593</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7391</v>
+        <v>0.7174</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6355</v>
+        <v>0.6286</v>
       </c>
     </row>
     <row r="8">
@@ -1151,16 +1151,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7188</v>
+        <v>0.7232</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5591</v>
+        <v>0.5652</v>
       </c>
       <c r="F7" t="n">
         <v>0.7027</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6228</v>
+        <v>0.6264999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1205,16 +1205,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.7321</v>
+        <v>0.7188</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5729</v>
+        <v>0.5567</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7432</v>
+        <v>0.7297</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6471</v>
+        <v>0.6316000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1370,13 +1370,13 @@
         <v>0.7383</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5574</v>
+        <v>0.5593</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7391</v>
+        <v>0.7174</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6355</v>
+        <v>0.6286</v>
       </c>
     </row>
     <row r="16">
